--- a/src/assets/Template Excel/Layout_Max_Capacity.xlsx
+++ b/src/assets/Template Excel/Layout_Max_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Worktools SRI\Frontend\sri_monthly_planning_fe\src\assets\Template Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D582A7-4DB0-4609-B92F-8296240330BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CE567B-0F0C-42BE-B0BC-612D961B6C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,13 +37,13 @@
     <t>NOMOR</t>
   </si>
   <si>
+    <t>PRODUCT_PART_NUMBER</t>
+  </si>
+  <si>
     <t>MACHINECURINGTYPE</t>
   </si>
   <si>
     <t>MAX_CAPACITY_ID</t>
-  </si>
-  <si>
-    <t>PART_NUMBER</t>
   </si>
 </sst>
 </file>
@@ -518,13 +518,13 @@
         <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>0</v>
